--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b09d15aee93034e6/Desktop/PythonProjects/Starrez/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B09D15AEE93034E6/Desktop/PythonProjects/Starrez/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CD4CE5C-B3BE-4990-919A-1ADFC7AD8244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{E0F4C090-53B0-4C9F-9CC7-814165066D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{6EED516B-0577-4310-9910-B143C4660298}"/>
   </bookViews>
@@ -39,25 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Bui</t>
-  </si>
-  <si>
-    <t>khbui@aim.com</t>
-  </si>
-  <si>
-    <t>Elaine</t>
-  </si>
-  <si>
-    <t>Oliquiano</t>
-  </si>
-  <si>
-    <t>Elaineo@outlook.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Rita</t>
   </si>
@@ -68,12 +50,6 @@
     <t>ritatimur@gmail.com</t>
   </si>
   <si>
-    <t>TIMUR</t>
-  </si>
-  <si>
-    <t>elaineo@outlook.com</t>
-  </si>
-  <si>
     <t>Christine</t>
   </si>
   <si>
@@ -117,18 +93,6 @@
   </si>
   <si>
     <t>tifflee51@gmail.com</t>
-  </si>
-  <si>
-    <t>Yolanda</t>
-  </si>
-  <si>
-    <t>Anderson</t>
-  </si>
-  <si>
-    <t>yolianderson@gmail.com</t>
-  </si>
-  <si>
-    <t>yolianderson2@gmail.com</t>
   </si>
   <si>
     <t>ferrarae@gmail.com</t>
@@ -265,6 +229,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -584,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEDB35E2-C8BA-42A7-8061-CF4629C26B52}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -594,13 +562,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -638,54 +606,54 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
         <v>19</v>
@@ -707,134 +675,69 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>